--- a/SOT_results/SOT_15deg.xlsx
+++ b/SOT_results/SOT_15deg.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>15° 模型数据（52点）</a:t>
+              <a:t>15° 模型数据（角度相关形状，52点）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -181,7 +181,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$A$2:$A$53</f>
+              <f>'Sheet1'!$A$2:$A$27</f>
             </numRef>
           </xVal>
           <yVal>
@@ -625,7 +625,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>11.98368188139051</v>
+        <v>13.17773356095276</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>11.92226872721165</v>
+        <v>12.37553560654939</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +641,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>11.91792089328749</v>
+        <v>11.73979992385841</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>11.91683393480644</v>
+        <v>11.80976015985502</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>11.91846437252801</v>
+        <v>11.93571315045511</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>11.91574697632541</v>
+        <v>11.9478811276776</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>11.91466001784436</v>
+        <v>11.88920660377777</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>11.92118176873062</v>
+        <v>11.88732083484917</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>11.91574697632541</v>
+        <v>11.88537602118982</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>11.92879047809791</v>
+        <v>11.87171128689949</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>11.92389916493321</v>
+        <v>11.8631872675331</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>11.91846437252801</v>
+        <v>11.86729511009491</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>11.92172524797114</v>
+        <v>11.86399387869406</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +729,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>11.92063828949009</v>
+        <v>11.86162158468165</v>
       </c>
     </row>
     <row r="16">
@@ -737,7 +737,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>11.92770351961686</v>
+        <v>11.85911265082287</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>11.93205135354103</v>
+        <v>12.26374055467733</v>
       </c>
     </row>
     <row r="18">
@@ -753,7 +753,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>11.92770351961686</v>
+        <v>12.96107597587945</v>
       </c>
     </row>
     <row r="19">
@@ -761,7 +761,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>11.93150787430051</v>
+        <v>13.37847210660041</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>11.93422527050312</v>
+        <v>13.40105990187159</v>
       </c>
     </row>
     <row r="21">
@@ -777,7 +777,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>11.93042091581947</v>
+        <v>13.38265288510657</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>11.93476874974364</v>
+        <v>13.30040617868298</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>11.93748614594624</v>
+        <v>13.16662217718366</v>
       </c>
     </row>
     <row r="24">
@@ -801,7 +801,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>11.94835573075665</v>
+        <v>12.36418399676562</v>
       </c>
     </row>
     <row r="25">
@@ -809,7 +809,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>11.99672538316301</v>
+        <v>12.96136472751776</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>12.19998661911781</v>
+        <v>13.3846467114349</v>
       </c>
     </row>
     <row r="27">
@@ -825,7 +825,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>12.43150877557969</v>
+        <v>12.97819424016057</v>
       </c>
     </row>
     <row r="28">
@@ -833,7 +833,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>12.34292165937479</v>
+        <v>13.33508912410903</v>
       </c>
     </row>
     <row r="29">
@@ -841,7 +841,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>12.38585651937594</v>
+        <v>13.51450552962682</v>
       </c>
     </row>
     <row r="30">
@@ -849,7 +849,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>12.39835654190791</v>
+        <v>13.3228734192533</v>
       </c>
     </row>
     <row r="31">
@@ -857,7 +857,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>12.42716094165552</v>
+        <v>13.71701415982138</v>
       </c>
     </row>
     <row r="32">
@@ -865,7 +865,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>12.42498702469343</v>
+        <v>13.75444519258381</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +873,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>12.42716094165552</v>
+        <v>13.49245611516705</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>12.43857400570645</v>
+        <v>12.57758148608428</v>
       </c>
     </row>
     <row r="35">
@@ -889,7 +889,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>12.43422617178228</v>
+        <v>12.43138673690372</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>12.44183488114958</v>
+        <v>12.42793374488073</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>12.45216098671948</v>
+        <v>12.4015762104699</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>12.44074792266854</v>
+        <v>12.39686177420067</v>
       </c>
     </row>
     <row r="39">
@@ -921,7 +921,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>12.44835663203583</v>
+        <v>12.3925818051007</v>
       </c>
     </row>
     <row r="40">
@@ -929,7 +929,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>12.45216098671948</v>
+        <v>12.39722479549429</v>
       </c>
     </row>
     <row r="41">
@@ -937,7 +937,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>12.4760740733024</v>
+        <v>12.39270635773545</v>
       </c>
     </row>
     <row r="42">
@@ -945,7 +945,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>12.45216098671948</v>
+        <v>12.38430999515282</v>
       </c>
     </row>
     <row r="43">
@@ -953,7 +953,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>12.4554218621626</v>
+        <v>12.38107977788297</v>
       </c>
     </row>
     <row r="44">
@@ -961,7 +961,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>12.45650882064364</v>
+        <v>12.36793737943099</v>
       </c>
     </row>
     <row r="45">
@@ -969,7 +969,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>12.4554218621626</v>
+        <v>12.49304017641562</v>
       </c>
     </row>
     <row r="46">
@@ -977,7 +977,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>12.45650882064364</v>
+        <v>12.73622306873994</v>
       </c>
     </row>
     <row r="47">
@@ -985,7 +985,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>12.45379142444104</v>
+        <v>12.91827225430441</v>
       </c>
     </row>
     <row r="48">
@@ -993,7 +993,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>12.45270446595999</v>
+        <v>13.00983049693937</v>
       </c>
     </row>
     <row r="49">
@@ -1001,7 +1001,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>12.45596534140313</v>
+        <v>12.61395046535296</v>
       </c>
     </row>
     <row r="50">
@@ -1009,7 +1009,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>12.44509575659271</v>
+        <v>12.52393337593741</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>12.39074783254062</v>
+        <v>12.73306025493985</v>
       </c>
     </row>
     <row r="52">
@@ -1025,7 +1025,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>12.1032473143051</v>
+        <v>13.29254570896565</v>
       </c>
     </row>
     <row r="53">
@@ -1033,7 +1033,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>11.80270329429707</v>
+        <v>13.46213911378534</v>
       </c>
     </row>
   </sheetData>
@@ -1074,11 +1074,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1144,84 +1144,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>电阻单位</t>
+          <t>翻转幅度A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>沿用原始文件数值；原始文件未注明纵轴单位</t>
+          <t>0.5263596444（保持前次角度模型）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>翻转幅度A</t>
+          <t>曲线形状</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.5263596444（按前次分析的平台差模型）</t>
+          <t>角度相关形状模板：0°/45°/75°实测回线归一化后按角度混合</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>中心基线</t>
+          <t>形状插值</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.18898116（由已测角度基线保形插值，仅用于保持绘图尺度）</t>
+          <t>0°→45°线性混合</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>曲线形状</t>
+          <t>纵轴单位</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>复用165°实测回线的两支路形状，按目标角度A缩放；未添加随机噪声</t>
+          <t>原始文件未注明，保留原始数值尺度</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>模型规律</t>
+          <t>实测区分</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0–90°单峰角度依赖；采用0°/45°/75°/90°实测幅度锚点的保形插值</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>实测区分</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>本文件不是该角度的实测记录；15°、30°、60°原始文件夹无实测数据，0°和45°文件也已按52点序列重新模型化</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>输入模板</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>165度.xlsx（用户上传）</t>
+          <t>本文件为模型生成数据；15°、30°、60°无原始OPJU，0°/45°为统一点数并按实测模板生成</t>
         </is>
       </c>
     </row>

--- a/SOT_results/SOT_15deg.xlsx
+++ b/SOT_results/SOT_15deg.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>15° 模型数据（角度相关形状，52点）</a:t>
+              <a:t>15° 标准双支路SOT模型（52点）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -625,7 +625,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>13.17773356095276</v>
+        <v>11.9258011778</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>12.37553560654939</v>
+        <v>11.9258011778</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +641,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>11.73979992385841</v>
+        <v>11.9258011778</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>11.80976015985502</v>
+        <v>11.92580117780001</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>11.93571315045511</v>
+        <v>11.92580117780004</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>11.9478811276776</v>
+        <v>11.92580117780022</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>11.88920660377777</v>
+        <v>11.92580117780111</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>11.88732083484917</v>
+        <v>11.92580117780578</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>11.88537602118982</v>
+        <v>11.92580117782999</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>11.87171128689949</v>
+        <v>11.92580117795572</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>11.8631872675331</v>
+        <v>11.92580117860846</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>11.86729511009491</v>
+        <v>11.92580118199728</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>11.86399387869406</v>
+        <v>11.92580119959096</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +729,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>11.86162158468165</v>
+        <v>11.92580129093184</v>
       </c>
     </row>
     <row r="16">
@@ -737,7 +737,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>11.85911265082287</v>
+        <v>11.92580176514466</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>12.26374055467733</v>
+        <v>11.92580422709577</v>
       </c>
     </row>
     <row r="18">
@@ -753,7 +753,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>12.96107597587945</v>
+        <v>11.92581700840688</v>
       </c>
     </row>
     <row r="19">
@@ -761,7 +761,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>13.37847210660041</v>
+        <v>11.92588335500683</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>13.40105990187159</v>
+        <v>11.92622753717346</v>
       </c>
     </row>
     <row r="21">
@@ -777,7 +777,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>13.38265288510657</v>
+        <v>11.9280072122887</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>13.30040617868298</v>
+        <v>11.93705648826432</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>13.16662217718366</v>
+        <v>11.97942850213443</v>
       </c>
     </row>
     <row r="24">
@@ -801,7 +801,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>12.36418399676562</v>
+        <v>12.1208985354515</v>
       </c>
     </row>
     <row r="25">
@@ -809,7 +809,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>12.96136472751776</v>
+        <v>12.322440545419</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>13.3846467114349</v>
+        <v>12.42096797572261</v>
       </c>
     </row>
     <row r="27">
@@ -825,7 +825,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>12.97819424016057</v>
+        <v>12.44585067323093</v>
       </c>
     </row>
     <row r="28">
@@ -833,7 +833,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>13.33508912410903</v>
+        <v>12.4521608222</v>
       </c>
     </row>
     <row r="29">
@@ -841,7 +841,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>13.51450552962682</v>
+        <v>12.4521608222</v>
       </c>
     </row>
     <row r="30">
@@ -849,7 +849,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>13.3228734192533</v>
+        <v>12.4521608222</v>
       </c>
     </row>
     <row r="31">
@@ -857,7 +857,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>13.71701415982138</v>
+        <v>12.45216082219999</v>
       </c>
     </row>
     <row r="32">
@@ -865,7 +865,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>13.75444519258381</v>
+        <v>12.45216082219996</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +873,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>13.49245611516705</v>
+        <v>12.45216082219979</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>12.57758148608428</v>
+        <v>12.45216082219889</v>
       </c>
     </row>
     <row r="35">
@@ -889,7 +889,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>12.43138673690372</v>
+        <v>12.45216082219422</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>12.42793374488073</v>
+        <v>12.45216082217001</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>12.4015762104699</v>
+        <v>12.45216082204428</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>12.39686177420067</v>
+        <v>12.45216082139154</v>
       </c>
     </row>
     <row r="39">
@@ -921,7 +921,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>12.3925818051007</v>
+        <v>12.45216081800272</v>
       </c>
     </row>
     <row r="40">
@@ -929,7 +929,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>12.39722479549429</v>
+        <v>12.45216080040904</v>
       </c>
     </row>
     <row r="41">
@@ -937,7 +937,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>12.39270635773545</v>
+        <v>12.45216070906816</v>
       </c>
     </row>
     <row r="42">
@@ -945,7 +945,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>12.38430999515282</v>
+        <v>12.45216023485534</v>
       </c>
     </row>
     <row r="43">
@@ -953,7 +953,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>12.38107977788297</v>
+        <v>12.45215777290423</v>
       </c>
     </row>
     <row r="44">
@@ -961,7 +961,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>12.36793737943099</v>
+        <v>12.45214499159312</v>
       </c>
     </row>
     <row r="45">
@@ -969,7 +969,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>12.49304017641562</v>
+        <v>12.45207864499317</v>
       </c>
     </row>
     <row r="46">
@@ -977,7 +977,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>12.73622306873994</v>
+        <v>12.45173446282654</v>
       </c>
     </row>
     <row r="47">
@@ -985,7 +985,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>12.91827225430441</v>
+        <v>12.4499547877113</v>
       </c>
     </row>
     <row r="48">
@@ -993,7 +993,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>13.00983049693937</v>
+        <v>12.44090551173568</v>
       </c>
     </row>
     <row r="49">
@@ -1001,7 +1001,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>12.61395046535296</v>
+        <v>12.39853349786557</v>
       </c>
     </row>
     <row r="50">
@@ -1009,7 +1009,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>12.52393337593741</v>
+        <v>12.25706346454851</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>12.73306025493985</v>
+        <v>12.055521454581</v>
       </c>
     </row>
     <row r="52">
@@ -1025,7 +1025,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>13.29254570896565</v>
+        <v>11.95699402427739</v>
       </c>
     </row>
     <row r="53">
@@ -1033,7 +1033,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>13.46213911378534</v>
+        <v>11.93211132676907</v>
       </c>
     </row>
   </sheetData>
@@ -1074,11 +1074,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>模型生成（非实测）</t>
+          <t>标准双支路模型生成（非实测）</t>
         </is>
       </c>
     </row>
@@ -1149,55 +1149,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.5263596444（保持前次角度模型）</t>
+          <t>0.5263596444</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>曲线形状</t>
+          <t>开关阈值Ic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>角度相关形状模板：0°/45°/75°实测回线归一化后按角度混合</t>
+          <t>±0.02750000 A（平滑角度模型）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>形状插值</t>
+          <t>开关宽度</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0°→45°线性混合</t>
+          <t>0.00170000 A（窄开关区）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>纵轴单位</t>
+          <t>曲线结构</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>原始文件未注明，保留原始数值尺度</t>
+          <t>支路1在+Ic由低平台翻到高平台；支路2在−Ic由高平台翻到低平台</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>噪声处理</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>未添加随机噪声；未使用原始回线端点噪声</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>实测区分</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>本文件为模型生成数据；15°、30°、60°无原始OPJU，0°/45°为统一点数并按实测模板生成</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>本文件是模型预测/标准化数据，不是该角度的原始实测记录</t>
         </is>
       </c>
     </row>
